--- a/splists_out/needs_revision/plotsbci_not_garwood_2026-03-30.xlsx
+++ b/splists_out/needs_revision/plotsbci_not_garwood_2026-03-30.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BC5"/>
+  <dimension ref="A1:BC8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1069,11 +1069,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>myr2fl</t>
+          <t>ficuob</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ficus obtusifolia</t>
         </is>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1085,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1101,37 +1106,32 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>bci25ha</t>
+          <t>bci50ha, bci25ha</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Myrtales</t>
+          <t>Rosales</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Myrtaceae</t>
+          <t>Moraceae</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Myrciaria</t>
+          <t>Ficus</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>floribunda</t>
+          <t>obtusifolia</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>(H. West ex Willd.) O. Berg</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>R. Pérez 2347 (PMA, SCZ)</t>
+          <t>Kunth</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1141,17 +1141,17 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Myrciaria floribunda</t>
+          <t>Ficus obtusifolia</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Myrciaria floribunda</t>
+          <t>Ficus obtusifolia</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>myr2fl</t>
+          <t>ficuob</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Myrciaria floribunda</t>
+          <t>Ficus obtusifolia</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>(H.West ex Willd.) O.Berg</t>
+          <t>Kunth</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>131815</t>
+          <t>2811522</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>599327-1</t>
+          <t>853317-1</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1196,47 +1196,47 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>131815</t>
+          <t>2811522</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>599327-1</t>
+          <t>853317-1</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>599327-1</t>
+          <t>853317-1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Myrciaria floribunda</t>
+          <t>Ficus obtusifolia</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Myrciaria floribunda</t>
+          <t>Ficus obtusifolia</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>(H.West ex Willd.) O.Berg</t>
+          <t>Kunth</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Myrtaceae</t>
+          <t>Moraceae</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Myrciaria</t>
+          <t>Ficus</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>floribunda</t>
+          <t>obtusifolia</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>shrub or tree</t>
+          <t>tree</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>MYRF</t>
+          <t>FIOB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Myrciaria floribunda</t>
+          <t>Ficus obtusifolia</t>
         </is>
       </c>
       <c r="AZ4" t="b">
@@ -1278,18 +1278,18 @@
         </is>
       </c>
       <c r="BB4">
-        <v>210</v>
+        <v>142</v>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>Myrciaria floribunda</t>
+          <t>Ficus obtusifolia</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unonpa</t>
+          <t>myr2fl</t>
         </is>
       </c>
       <c r="C5">
@@ -1302,11 +1302,11 @@
         <v>0</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
       <c r="H5">
         <v>0</v>
       </c>
@@ -1321,37 +1321,37 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Zetek</t>
+          <t>bci25ha</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Magnoliales</t>
+          <t>Myrtales</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Annonaceae</t>
+          <t>Myrtaceae</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Unonopsis</t>
+          <t>Myrciaria</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>panamensis</t>
+          <t>floribunda</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>R.E. Fr.</t>
+          <t>(H. West ex Willd.) O. Berg</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>R. Pérez 2303 (PMA, SCZ)</t>
+          <t>R. Pérez 2347 (PMA, SCZ)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Unonopsis panamensis</t>
+          <t>Myrciaria floribunda</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Unonopsis panamensis</t>
+          <t>Myrciaria floribunda</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>unonpa</t>
+          <t>myr2fl</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Unonopsis panamensis</t>
+          <t>Myrciaria floribunda</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>R.E.Fr.</t>
+          <t>(H.West ex Willd.) O.Berg</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2447472</t>
+          <t>131815</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>259517-2</t>
+          <t>599327-1</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1416,47 +1416,47 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2447472</t>
+          <t>131815</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>259517-2</t>
+          <t>599327-1</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>259517-2</t>
+          <t>599327-1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Unonopsis panamensis</t>
+          <t>Myrciaria floribunda</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Unonopsis panamensis</t>
+          <t>Myrciaria floribunda</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>R.E.Fr.</t>
+          <t>(H.West ex Willd.) O.Berg</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>Annonaceae</t>
+          <t>Myrtaceae</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Unonopsis</t>
+          <t>Myrciaria</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>panamensis</t>
+          <t>floribunda</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>tree</t>
+          <t>shrub or tree</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>UNO2</t>
+          <t>MYRF</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Unonopsis panamensis</t>
+          <t>Myrciaria floribunda</t>
         </is>
       </c>
       <c r="AZ5" t="b">
@@ -1498,9 +1498,674 @@
         </is>
       </c>
       <c r="BB5">
+        <v>210</v>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>Myrciaria floribunda</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>pipecu</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Piper culebranum</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>bci50ha, P11</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Piperales</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Piperaceae</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Piper</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>colonense</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>C. DC.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Piper colonense</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Piper colonense</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>pipecu</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Piper colonense</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>C.DC.</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2557497</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>197627-2</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>2557497</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>197627-2</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>197627-2</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Piper colonense</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Piper colonense</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>C.DC.</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Piperaceae</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Piper</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>colonense</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>shrub or tree</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>PPCU</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Piper colonense</t>
+        </is>
+      </c>
+      <c r="AZ6" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>Plots_census</t>
+        </is>
+      </c>
+      <c r="BB6">
+        <v>240</v>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>Piper colonense</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>quaras</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quararibea asterolepis</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>2417</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>21</v>
+      </c>
+      <c r="H7">
+        <v>44</v>
+      </c>
+      <c r="I7">
+        <v>31</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>73</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>bci50ha, bci10ha, bci25ha, P14, P11, Zetek, AVA, Drayton, Pearson</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Malvales</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Malvaceae</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Quararibea</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>stenophylla</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Pittier</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>R. Pérez 2042 (PMA, SCZ)</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Quararibea stenophylla</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Quararibea stenophylla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>quaras</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Quararibea stenophylla</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Pittier</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2868400</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>215426-2</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>2868400</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>215426-2</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>215426-2</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Quararibea stenophylla</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Quararibea stenophylla</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Pittier</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>Malvaceae</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Quararibea</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>stenophylla</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>QUA1</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Quararibea stenophylla</t>
+        </is>
+      </c>
+      <c r="AZ7" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Plots_census</t>
+        </is>
+      </c>
+      <c r="BB7">
+        <v>272</v>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>Quararibea stenophylla</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>unonpa</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Zetek</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Magnoliales</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Annonaceae</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Unonopsis</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>panamensis</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>R.E. Fr.</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>R. Pérez 2303 (PMA, SCZ)</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Freestanding</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Unonopsis panamensis</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Unonopsis panamensis</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>unonpa</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Unonopsis panamensis</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>R.E.Fr.</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2447472</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>259517-2</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>2447472</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>259517-2</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>259517-2</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Unonopsis panamensis</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Unonopsis panamensis</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>R.E.Fr.</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Annonaceae</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Unonopsis</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>panamensis</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>tree</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>UNO2</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Unonopsis panamensis</t>
+        </is>
+      </c>
+      <c r="AZ8" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>Plots_census</t>
+        </is>
+      </c>
+      <c r="BB8">
         <v>315</v>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>Unonopsis panamensis</t>
         </is>
